--- a/public/templates/test_input/Input_bao_cao_12.xlsx
+++ b/public/templates/test_input/Input_bao_cao_12.xlsx
@@ -759,199 +759,109 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ca 1</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>PX Khai thác 3</t>
+          <t>PX Khai thác 1</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Phạm Văn D</t>
+          <t>Hoàng Văn E</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>163</v>
+        <v>1150</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>9.5</v>
+        <v>10.9</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>4.9</v>
+        <v>11.2</v>
       </c>
       <c r="J4" s="28" t="n">
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="L4" s="28" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
       <c r="N4" s="28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P4" s="28" t="n">
         <v>7.5</v>
       </c>
-      <c r="O4" s="28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P4" s="28" t="n">
-        <v>7.4</v>
-      </c>
       <c r="Q4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="12" t="inlineStr">
         <is>
-          <t>Máy khoan gặp sự cố, tiến độ chậm.</t>
+          <t>Mất điện cục bộ 30 phút.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Ca 3</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>PX Khai thác 1</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Phạm Văn D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>394</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J5" s="28" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K5" s="28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L5" s="28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M5" s="28" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="N5" s="28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O5" s="28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P5" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="12" t="inlineStr"/>
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Ca 3</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>PX Khai thác 3</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn A</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>967</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J6" s="28" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K6" s="28" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="L6" s="28" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M6" s="28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N6" s="28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O6" s="28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P6" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>Điều kiện sản xuất ổn định.</t>
-        </is>
-      </c>
+      <c r="A6" s="27" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="28" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="28" t="n"/>
+      <c r="N6" s="28" t="n"/>
+      <c r="O6" s="28" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="27" t="n"/>
